--- a/Assets/Project/Csv/MagicalEggs.xlsx
+++ b/Assets/Project/Csv/MagicalEggs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\GitLab\Dairy Farm\Assets\Project\Csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B90557EF-7B04-4C30-AD22-8307F30CDA91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBA5A439-2E00-45C3-8E14-4B37625EABC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2970" yWindow="2640" windowWidth="21600" windowHeight="11295" xr2:uid="{F5EC58A1-2CB0-4597-AD94-4C4B1A7FFC79}"/>
+    <workbookView xWindow="1800" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{F5EC58A1-2CB0-4597-AD94-4C4B1A7FFC79}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
